--- a/04_DESIGN_TABLES/DesignTable_2505_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2505_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,169 @@
       <c r="AU2" t="inlineStr">
         <is>
           <t>2505-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2505-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="L3" t="n">
+        <v>60</v>
+      </c>
+      <c r="M3" t="n">
+        <v>37</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.50468</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2505-06-06-FG</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>45 deg Male JIC x Female Pipe Elbow, 3/8-18 NPTF (female) x 9/16-18 JIC</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2505</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>9/16-18 JIC</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; legs / flats / bore: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.27, one source); tap drill = Air-Way per size (A1); JIC end MS33656J | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries = Air-Way's per-size value; user 2026-10-08 'reuse end details - yes'), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only); the row's PORTDEPTH only where the row carries one - said in $COMMENT); connecting drill to the axis crossing = the tap drill carried to the crossing (MEASURED: Brennan 2505-08-08-FG STEP - the 0.718 drill runs from the bottom of the 0.75 deep tapered port to the axis crossing; the tapered port itself and its 45deg mouth chamfer are drawn as the tap-drill cylinder + the Thread feature, as on every built female port); each leg bore runs from its face to the axis crossing; Brennan 2505-08-08-FG STEP (2026-10-02, tools/measure/forged.py): JIC leg tip 1.040, its hex arm ends 0.383 (= M - the 2403 -08 JIC end length 0.657), JIC end = the 2403 -08 chain INCLUDING the thread relief (0.094 at the cone dia + 60deg ramp); female leg face 0.940, hex arm to 0.680 then the round collar 0.260 at the flats dia; A/F 1.062, corner puck radius 0.6131 = the hex corner radius, flats normal to Z, legs 135 deg apart = the gen_tee e45 pattern (Brennan draws the JIC leg on -X and the port at 45 deg - the same part turned)</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; legs / flats / bore from OMi Items (= Brennan TFA p.27, one source); end details from the end library | leg 1: female port thread length = MS51503 P1 0.68 (library) - the row has no measured PORTDEPTH@BORE; leg 2: inner thread edge clears the corner puck by only 0.0090</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2505-06-06-FG</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_2505_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2505_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU3"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,38 +651,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2505-12-12-FG</t>
+          <t>2505-08-08-FG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.656</v>
+        <v>0.531</v>
       </c>
       <c r="D2" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="E2" t="n">
-        <v>0.656</v>
+        <v>0.531</v>
       </c>
       <c r="F2" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="G2" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="L2" t="n">
         <v>60</v>
@@ -691,88 +691,88 @@
         <v>37</v>
       </c>
       <c r="N2" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.609</v>
+        <v>0.391</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="R2" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="S2" t="n">
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
       <c r="T2" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="V2" t="n">
-        <v>0.51214</v>
+        <v>0.40714</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.312</v>
+        <v>1.062</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.787</v>
+        <v>0.68</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.312</v>
+        <v>1.062</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.556</v>
+        <v>0.383</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.656</v>
+        <v>0.531</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.656</v>
+        <v>0.531</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.37824</v>
+        <v>0.30607</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.37824</v>
+        <v>0.30607</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.75698</v>
+        <v>0.61265</v>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2505-12-12-FG</t>
+          <t>2505-08-08-FG</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Female Pipe Elbow, 3/4-14 NPTF (female) x 1 1/16-12 JIC</t>
+          <t>45 deg Male JIC x Female Pipe Elbow, 1/2-14 NPTF (female) x 3/4-16 JIC</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -797,17 +797,17 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / Hex Flat / Side 1 ID = JIC leg / female pipe leg / body hex / JIC bore (Brennan TFA catalog p27 drawing M / N / Y / B1; Brennan 2505-08-08-FG STEP: JIC tip 1.040, female face 0.940, A/F 1.062, bore 0.391 = OMi row 793)); OMi = Brennan data (Brennan catalog TFA p27 (MJ-FP 45 DEG ELBOW) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2505-12-12 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): TAPDRILL@BORE: end-library tap drill of the -12 pipe port = 0.91 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries = Air-Way's per-size value; user 2026-10-08 'reuse end details - yes'), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only); the row's PORTDEPTH only where the row carries one - said in $COMMENT); connecting drill to the axis crossing = the tap drill carried to the crossing (MEASURED: Brennan 2505-08-08-FG STEP - the 0.718 drill runs from the bottom of the 0.75 deep tapered port to the axis crossing; the tapered port itself and its 45deg mouth chamfer are drawn as the tap-drill cylinder + the Thread feature, as on every built female port); each leg bore runs from its face to the axis crossing; Brennan 2505-08-08-FG STEP (2026-10-02, tools/measure/forged.py): JIC leg tip 1.040, its hex arm ends 0.383 (= M - the 2403 -08 JIC end length 0.657), JIC end = the 2403 -08 chain INCLUDING the thread relief (0.094 at the cone dia + 60deg ramp); female leg face 0.940, hex arm to 0.680 then the round collar 0.260 at the flats dia; A/F 1.062, corner puck radius 0.6131 = the hex corner radius, flats normal to Z, legs 135 deg apart = the gen_tee e45 pattern (Brennan draws the JIC leg on -X and the port at 45 deg - the same part turned)</t>
+          <t>[BRENNAN-CELL 2026-10-21: PORTDEPTH@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2505-08-08 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): M2@DRIVE: OMi Items row 793 M 1 Size = 1.040; N6@DRIVE: OMi Items row 793 M 2 Size = 0.940; Y1@HEX: OMi Items row 793 Hex Flat = 1.062; D@BORE: OMi Items row 793 Side 1 ID = 0.391; THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library); THDMAJ_A@DRIVE: 1/2-14 -&gt; 0.84 (end library); TAPDRILL@BORE: end-library tap drill of the -08 pipe port = 0.7 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED | PORTDEPTH@BORE: Brennan port depth -08 = 0.750 measured on this part's own STEP 09_STEP_FILES/BRENNAN_2505-08-08-FG.stp (forged.py NPTFF leg at 45 deg: taper depth from the face 0.75, mouth 0.0315; brennan_port_depths.run 0.7500; C_ownstep/measure/2505-08-08-FG.txt) = the -08 value of gen_tee ANGLED_P1_NOTE (Q-ANGLED-P1, settled from the Brennan STEPs 2026-10-18: the MS51503 P1 0.90 does not fit the 0.94 leg of the 45 deg elbow) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries = Air-Way's per-size value; user 2026-10-08 'reuse end details - yes'), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only); the row's PORTDEPTH only where the row carries one - said in $COMMENT); connecting drill to the axis crossing = the tap drill carried to the crossing (MEASURED: Brennan 2505-08-08-FG STEP - the 0.718 drill runs from the bottom of the 0.75 deep tapered port to the axis crossing; the tapered port itself and its 45deg mouth chamfer are drawn as the tap-drill cylinder + the Thread feature, as on every built female port); each leg bore runs from its face to the axis crossing; Brennan 2505-08-08-FG STEP (2026-10-02, tools/measure/forged.py): JIC leg tip 1.040, its hex arm ends 0.383 (= M - the 2403 -08 JIC end length 0.657), JIC end = the 2403 -08 chain INCLUDING the thread relief (0.094 at the cone dia + 60deg ramp); female leg face 0.940, hex arm to 0.680 then the round collar 0.260 at the flats dia; A/F 1.062, corner puck radius 0.6131 = the hex corner radius, flats normal to Z, legs 135 deg apart = the gen_tee e45 pattern (Brennan draws the JIC leg on -X and the port at 45 deg - the same part turned)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>2026-10-02 (JIC-TEES): stays MISSING ONLY for the female port (TAPDRILL@BORE, PORTDEPTH@BORE): OMi / the catalog print no tap drill and no Brennan STEP of this part is in the repo - every other cell is now filled from OMi (Q-TRANSFER-TAPDRILL; candidates in proposals/) | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2505-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): the female port now takes the end-library tap drill and MS51503 P1 - ASSUMED (one source) | leg 1: female port thread length = MS51503 P1 0.91 (library) - the row has no measured PORTDEPTH@BORE</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2505-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): body from OMi Items row 793, ports from the end library (not from its own Brennan file) - ASSUMED (one source) | 2026-10-21 batch 19 C (staged): PORTDEPTH@BORE 0.75 from the own Brennan STEP (Q-ANGLED-P1); the body stays OMi Items row 793 | Brennan 2505-08-08-FG STEP (2026-10-02, tools/measure/forged.py): JIC tip 1.040 = OMi M 1; female face 0.940 = OMi M 2; A/F 1.062 = OMi; JIC bore 0.391 = OMi; JIC hex arm to 0.383 and chain = 2403 -08 incl. the relief; port: collar 0.260, tapered port 0.75 deep (minor 0.747 -&gt; 0.792 dia, 45deg mouth to 0.855), drill 0.718 from the port bottom to the crossing (= TAPDRILL / PORTDEPTH of this row); volume 0.94759 in^3</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2505-12-12-FG</t>
+          <t>2505-08-08-FG</t>
         </is>
       </c>
     </row>
@@ -971,6 +971,169 @@
       <c r="AU3" t="inlineStr">
         <is>
           <t>2505-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2505-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="L4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M4" t="n">
+        <v>37</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.75698</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2505-12-12-FG</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>45 deg Male JIC x Female Pipe Elbow, 3/4-14 NPTF (female) x 1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>2505</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / Hex Flat / Side 1 ID = JIC leg / female pipe leg / body hex / JIC bore (Brennan TFA catalog p27 drawing M / N / Y / B1; Brennan 2505-08-08-FG STEP: JIC tip 1.040, female face 0.940, A/F 1.062, bore 0.391 = OMi row 793)); OMi = Brennan data (Brennan catalog TFA p27 (MJ-FP 45 DEG ELBOW) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2505-12-12 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): TAPDRILL@BORE: end-library tap drill of the -12 pipe port = 0.91 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries = Air-Way's per-size value; user 2026-10-08 'reuse end details - yes'), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only); the row's PORTDEPTH only where the row carries one - said in $COMMENT); connecting drill to the axis crossing = the tap drill carried to the crossing (MEASURED: Brennan 2505-08-08-FG STEP - the 0.718 drill runs from the bottom of the 0.75 deep tapered port to the axis crossing; the tapered port itself and its 45deg mouth chamfer are drawn as the tap-drill cylinder + the Thread feature, as on every built female port); each leg bore runs from its face to the axis crossing; Brennan 2505-08-08-FG STEP (2026-10-02, tools/measure/forged.py): JIC leg tip 1.040, its hex arm ends 0.383 (= M - the 2403 -08 JIC end length 0.657), JIC end = the 2403 -08 chain INCLUDING the thread relief (0.094 at the cone dia + 60deg ramp); female leg face 0.940, hex arm to 0.680 then the round collar 0.260 at the flats dia; A/F 1.062, corner puck radius 0.6131 = the hex corner radius, flats normal to Z, legs 135 deg apart = the gen_tee e45 pattern (Brennan draws the JIC leg on -X and the port at 45 deg - the same part turned)</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>2026-10-02 (JIC-TEES): stays MISSING ONLY for the female port (TAPDRILL@BORE, PORTDEPTH@BORE): OMi / the catalog print no tap drill and no Brennan STEP of this part is in the repo - every other cell is now filled from OMi (Q-TRANSFER-TAPDRILL; candidates in proposals/) | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2505-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): the female port now takes the end-library tap drill and MS51503 P1 - ASSUMED (one source) | leg 1: female port thread length = MS51503 P1 0.91 (library) - the row has no measured PORTDEPTH@BORE</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2505-12-12-FG</t>
         </is>
       </c>
     </row>
